--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CB BOET MATARÓ.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CB BOET MATARÓ.xlsx
@@ -565,13 +565,13 @@
         <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>9.259899999999998</v>
+        <v>21.1948</v>
       </c>
       <c r="E2" t="n">
-        <v>12.5393</v>
+        <v>20.7809</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.279399999999999</v>
+        <v>0.4139000000000004</v>
       </c>
       <c r="G2" t="n">
         <v>14.5436</v>
@@ -610,13 +610,13 @@
         <v>48.6043</v>
       </c>
       <c r="S2" t="n">
-        <v>-24.7164</v>
+        <v>-12.7818</v>
       </c>
       <c r="T2" t="n">
-        <v>-15.024</v>
+        <v>-6.7825</v>
       </c>
       <c r="U2" t="n">
-        <v>-9.692600000000001</v>
+        <v>-5.9992</v>
       </c>
       <c r="V2" t="n">
         <v>17.449</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8651</v>
+        <v>1.911</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1827</v>
+        <v>1.2847</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6824</v>
+        <v>0.6263</v>
       </c>
       <c r="G3" t="n">
         <v>1.7892</v>
@@ -688,13 +688,13 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0759</v>
+        <v>0.1219</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0623</v>
+        <v>0.0397</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1383</v>
+        <v>0.0822</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. BONET TORRALBA</t>
+          <t>E. SANCHEZ MASEDO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4565999999999997</v>
+        <v>-0.4677</v>
       </c>
       <c r="E4" t="n">
-        <v>-11.898</v>
+        <v>-0.458</v>
       </c>
       <c r="F4" t="n">
-        <v>12.3545</v>
+        <v>-0.0097</v>
       </c>
       <c r="G4" t="n">
-        <v>-6.726899999999999</v>
+        <v>0.1558</v>
       </c>
       <c r="H4" t="n">
-        <v>-6.2079</v>
+        <v>-0.2924</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5190000000000003</v>
+        <v>0.4483</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.6396</v>
+        <v>0.0805</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.2188</v>
+        <v>0.0403</v>
       </c>
       <c r="L4" t="n">
-        <v>1.5791</v>
+        <v>0.0402</v>
       </c>
       <c r="M4" t="n">
-        <v>-5.0876</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.9893</v>
+        <v>-0.3328</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.0981</v>
+        <v>0.4081</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1983000000000001</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q4" t="n">
-        <v>-16.2674</v>
+        <v>-0.9919</v>
       </c>
       <c r="R4" t="n">
-        <v>16.0691</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>8.8774</v>
+        <v>0.3684</v>
       </c>
       <c r="T4" t="n">
-        <v>3.6343</v>
+        <v>0.4535</v>
       </c>
       <c r="U4" t="n">
-        <v>5.243</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.4955</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>2.3746</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-3.8701</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. SANCHEZ MASEDO</t>
+          <t>E. LAGUARDA ROQUEÑI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.9483</v>
+        <v>-0.5669</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8264</v>
+        <v>-0.3137</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1219</v>
+        <v>-0.2532</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1558</v>
+        <v>-0.2594</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2924</v>
+        <v>0.0955</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4483</v>
+        <v>-0.355</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0805</v>
+        <v>0.0603</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0403</v>
+        <v>0.0202</v>
       </c>
       <c r="L5" t="n">
         <v>0.0402</v>
       </c>
       <c r="M5" t="n">
+        <v>-0.3198</v>
+      </c>
+      <c r="N5" t="n">
         <v>0.07530000000000001</v>
       </c>
-      <c r="N5" t="n">
-        <v>-0.3328</v>
-      </c>
       <c r="O5" t="n">
-        <v>0.4081</v>
+        <v>-0.3951</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9919</v>
+        <v>0.1984</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.1984</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1122</v>
+        <v>-0.5059</v>
       </c>
       <c r="T5" t="n">
-        <v>0.08500000000000001</v>
+        <v>-0.3741</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1973</v>
+        <v>-0.1318</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. LAGUARDA ROQUEÑI</t>
+          <t>E. ROMERO AGUERA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,61 +874,61 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0592</v>
+        <v>-0.6194999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3137</v>
+        <v>0.2865</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7455000000000001</v>
+        <v>-0.906</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2594</v>
+        <v>-0.9879</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0955</v>
+        <v>0.1055</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.355</v>
+        <v>-1.0935</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0603</v>
+        <v>0.7284999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0202</v>
+        <v>0.7662</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0402</v>
+        <v>-0.03760000000000008</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3198</v>
+        <v>-1.7165</v>
       </c>
       <c r="N6" t="n">
-        <v>0.07530000000000001</v>
+        <v>-0.6606</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3951</v>
+        <v>-1.0559</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1984</v>
+        <v>1.3887</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1984</v>
+        <v>1.3887</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9982</v>
+        <v>-1.0203</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3741</v>
+        <v>-0.4421</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6241</v>
+        <v>-0.5782</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2353</v>
+        <v>-0.919</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1044</v>
+        <v>0.3084</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.3397</v>
+        <v>-1.2275</v>
       </c>
       <c r="G7" t="n">
         <v>0.07200000000000001</v>
@@ -1000,13 +1000,13 @@
         <v>0.5952</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.696</v>
+        <v>-0.3797</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5611</v>
+        <v>-0.357</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1349</v>
+        <v>-0.0227</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2065</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. ROMERO AGUERA</t>
+          <t>O. JIMENEZ ROCA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3371</v>
+        <v>-1.5766</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2066</v>
+        <v>-0.2494</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1304</v>
+        <v>-1.3272</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9879</v>
+        <v>-0.9295</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1055</v>
+        <v>-0.8064</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.0935</v>
+        <v>-0.1231</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7284999999999999</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7662</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.03760000000000008</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.7165</v>
+        <v>-0.9295</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6606</v>
+        <v>-0.8064</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.0559</v>
+        <v>-0.1231</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3887</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3887</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.7378</v>
+        <v>-0.3812</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9352</v>
+        <v>-0.2494</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8026</v>
+        <v>-0.1318</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O. JIMENEZ ROCA</t>
+          <t>B. BONET TORRALBA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,70 +1108,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6608</v>
+        <v>-5.966600000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2494</v>
+        <v>-16.155</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4114</v>
+        <v>10.1885</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9295</v>
+        <v>-6.726899999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8064</v>
+        <v>-6.2079</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1231</v>
+        <v>-0.5190000000000003</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-1.6396</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>-3.2188</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.5791</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9295</v>
+        <v>-5.0876</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8064</v>
+        <v>-2.9893</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1231</v>
+        <v>-2.0981</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0.1983000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-16.2674</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>16.0691</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4653</v>
+        <v>2.4542</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2494</v>
+        <v>-0.6224999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2159</v>
+        <v>3.077</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.266</v>
+        <v>-1.4955</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.3746</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.266</v>
+        <v>-3.8701</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.9072</v>
+        <v>-6.9142</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.971</v>
+        <v>-5.5628</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9363</v>
+        <v>-1.3514</v>
       </c>
       <c r="G10" t="n">
         <v>-6.3804</v>
@@ -1234,13 +1234,13 @@
         <v>2.579</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1461</v>
+        <v>-0.153</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7537</v>
+        <v>-0.3456</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3923</v>
+        <v>0.1926</v>
       </c>
       <c r="V10" t="n">
         <v>1.008</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. ESONO MBA</t>
+          <t>E. NOGUES MARTIN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D11" t="n">
-        <v>-16.6972</v>
+        <v>-12.9169</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.530200000000001</v>
+        <v>-11.2086</v>
       </c>
       <c r="F11" t="n">
-        <v>-13.167</v>
+        <v>-1.708099999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-15.2943</v>
+        <v>-15.1639</v>
       </c>
       <c r="H11" t="n">
-        <v>-7.811200000000001</v>
+        <v>-17.8561</v>
       </c>
       <c r="I11" t="n">
-        <v>-7.482900000000001</v>
+        <v>2.691800000000002</v>
       </c>
       <c r="J11" t="n">
-        <v>2.4129</v>
+        <v>22.5693</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.7199</v>
+        <v>6.0628</v>
       </c>
       <c r="L11" t="n">
-        <v>3.1327</v>
+        <v>16.5065</v>
       </c>
       <c r="M11" t="n">
-        <v>-17.7069</v>
+        <v>-37.7335</v>
       </c>
       <c r="N11" t="n">
-        <v>-7.0913</v>
+        <v>-23.9191</v>
       </c>
       <c r="O11" t="n">
-        <v>-10.6155</v>
+        <v>-13.8143</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3968999999999996</v>
+        <v>6.5468</v>
       </c>
       <c r="Q11" t="n">
-        <v>-30.749</v>
+        <v>-49.5958</v>
       </c>
       <c r="R11" t="n">
-        <v>31.1465</v>
+        <v>56.1424</v>
       </c>
       <c r="S11" t="n">
-        <v>20.9183</v>
+        <v>-15.8155</v>
       </c>
       <c r="T11" t="n">
-        <v>20.7648</v>
+        <v>-9.7974</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1538999999999999</v>
+        <v>-6.0182</v>
       </c>
       <c r="V11" t="n">
-        <v>-22.7184</v>
+        <v>11.5163</v>
       </c>
       <c r="W11" t="n">
-        <v>4.0418</v>
+        <v>25.6155</v>
       </c>
       <c r="X11" t="n">
-        <v>-26.7602</v>
+        <v>-14.0994</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. DIEZ VALERO</t>
+          <t>P. MORENO MARTIN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>23</v>
       </c>
       <c r="D12" t="n">
-        <v>-16.7041</v>
+        <v>-18.3793</v>
       </c>
       <c r="E12" t="n">
-        <v>-21.8162</v>
+        <v>-5.6274</v>
       </c>
       <c r="F12" t="n">
-        <v>5.111899999999999</v>
+        <v>-12.7518</v>
       </c>
       <c r="G12" t="n">
-        <v>-9.9739</v>
+        <v>-4.0348</v>
       </c>
       <c r="H12" t="n">
-        <v>-8.512799999999999</v>
+        <v>-3.2194</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.461099999999999</v>
+        <v>-0.8155999999999998</v>
       </c>
       <c r="J12" t="n">
-        <v>12.7629</v>
+        <v>3.7909</v>
       </c>
       <c r="K12" t="n">
-        <v>9.154</v>
+        <v>1.8028</v>
       </c>
       <c r="L12" t="n">
-        <v>3.6089</v>
+        <v>1.9883</v>
       </c>
       <c r="M12" t="n">
-        <v>-22.7365</v>
+        <v>-7.8264</v>
       </c>
       <c r="N12" t="n">
-        <v>-17.6669</v>
+        <v>-5.022</v>
       </c>
       <c r="O12" t="n">
-        <v>-5.0702</v>
+        <v>-2.8036</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.388500000000001</v>
+        <v>5.5548</v>
       </c>
       <c r="Q12" t="n">
-        <v>-39.4783</v>
+        <v>-13.0932</v>
       </c>
       <c r="R12" t="n">
-        <v>38.0897</v>
+        <v>18.6484</v>
       </c>
       <c r="S12" t="n">
-        <v>2.3178</v>
+        <v>-9.511200000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>2.025999999999999</v>
+        <v>-1.9489</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2920000000000005</v>
+        <v>-7.5623</v>
       </c>
       <c r="V12" t="n">
-        <v>-7.659400000000001</v>
+        <v>-10.3877</v>
       </c>
       <c r="W12" t="n">
-        <v>2.8736</v>
+        <v>5.624</v>
       </c>
       <c r="X12" t="n">
-        <v>-10.5327</v>
+        <v>-16.0114</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E. NOGUES MARTIN</t>
+          <t>I. VILLAR CANTERO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>22</v>
       </c>
       <c r="D13" t="n">
-        <v>-19.0172</v>
+        <v>-21.915</v>
       </c>
       <c r="E13" t="n">
-        <v>-19.0306</v>
+        <v>-10.5624</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01329999999999987</v>
+        <v>-11.3525</v>
       </c>
       <c r="G13" t="n">
-        <v>-15.1639</v>
+        <v>-14.4272</v>
       </c>
       <c r="H13" t="n">
-        <v>-17.8561</v>
+        <v>-2.3087</v>
       </c>
       <c r="I13" t="n">
-        <v>2.691800000000002</v>
+        <v>-12.1186</v>
       </c>
       <c r="J13" t="n">
-        <v>22.5693</v>
+        <v>11.8584</v>
       </c>
       <c r="K13" t="n">
-        <v>6.0628</v>
+        <v>14.3918</v>
       </c>
       <c r="L13" t="n">
-        <v>16.5065</v>
+        <v>-2.5334</v>
       </c>
       <c r="M13" t="n">
-        <v>-37.7335</v>
+        <v>-26.2859</v>
       </c>
       <c r="N13" t="n">
-        <v>-23.9191</v>
+        <v>-16.7004</v>
       </c>
       <c r="O13" t="n">
-        <v>-13.8143</v>
+        <v>-9.5855</v>
       </c>
       <c r="P13" t="n">
-        <v>6.5468</v>
+        <v>6.7451</v>
       </c>
       <c r="Q13" t="n">
-        <v>-49.5958</v>
+        <v>-27.1786</v>
       </c>
       <c r="R13" t="n">
-        <v>56.1424</v>
+        <v>33.9237</v>
       </c>
       <c r="S13" t="n">
-        <v>-21.9163</v>
+        <v>-16.1836</v>
       </c>
       <c r="T13" t="n">
-        <v>-17.6194</v>
+        <v>-5.5302</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.2967</v>
+        <v>-10.6537</v>
       </c>
       <c r="V13" t="n">
-        <v>11.5163</v>
+        <v>1.9511</v>
       </c>
       <c r="W13" t="n">
-        <v>25.6155</v>
+        <v>10.288</v>
       </c>
       <c r="X13" t="n">
-        <v>-14.0994</v>
+        <v>-8.3369</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. MORENO MARTIN</t>
+          <t>A. DIEZ VALERO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>23</v>
       </c>
       <c r="D14" t="n">
-        <v>-23.2785</v>
+        <v>-25.949</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.2653</v>
+        <v>-27.66</v>
       </c>
       <c r="F14" t="n">
-        <v>-16.0134</v>
+        <v>1.7114</v>
       </c>
       <c r="G14" t="n">
-        <v>-4.0348</v>
+        <v>-9.9739</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.2194</v>
+        <v>-8.512799999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8155999999999998</v>
+        <v>-1.461099999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>3.7909</v>
+        <v>12.7629</v>
       </c>
       <c r="K14" t="n">
-        <v>1.8028</v>
+        <v>9.154</v>
       </c>
       <c r="L14" t="n">
-        <v>1.9883</v>
+        <v>3.6089</v>
       </c>
       <c r="M14" t="n">
-        <v>-7.8264</v>
+        <v>-22.7365</v>
       </c>
       <c r="N14" t="n">
-        <v>-5.022</v>
+        <v>-17.6669</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.8036</v>
+        <v>-5.0702</v>
       </c>
       <c r="P14" t="n">
-        <v>5.5548</v>
+        <v>-1.388500000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-13.0932</v>
+        <v>-39.4783</v>
       </c>
       <c r="R14" t="n">
-        <v>18.6484</v>
+        <v>38.0897</v>
       </c>
       <c r="S14" t="n">
-        <v>-14.4107</v>
+        <v>-6.9267</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.5871</v>
+        <v>-3.8184</v>
       </c>
       <c r="U14" t="n">
-        <v>-10.8235</v>
+        <v>-3.1087</v>
       </c>
       <c r="V14" t="n">
-        <v>-10.3877</v>
+        <v>-7.659400000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>5.624</v>
+        <v>2.8736</v>
       </c>
       <c r="X14" t="n">
-        <v>-16.0114</v>
+        <v>-10.5327</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>22</v>
       </c>
       <c r="D15" t="n">
-        <v>-35.2346</v>
+        <v>-30.1004</v>
       </c>
       <c r="E15" t="n">
-        <v>-19.5427</v>
+        <v>-17.5248</v>
       </c>
       <c r="F15" t="n">
-        <v>-15.6924</v>
+        <v>-12.5754</v>
       </c>
       <c r="G15" t="n">
         <v>-20.1851</v>
@@ -1624,13 +1624,13 @@
         <v>35.9074</v>
       </c>
       <c r="S15" t="n">
-        <v>-17.029</v>
+        <v>-11.8946</v>
       </c>
       <c r="T15" t="n">
-        <v>-7.2136</v>
+        <v>-5.1958</v>
       </c>
       <c r="U15" t="n">
-        <v>-9.8154</v>
+        <v>-6.698799999999999</v>
       </c>
       <c r="V15" t="n">
         <v>-8.138199999999999</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. VILLAR CANTERO</t>
+          <t>M. GARCIA IBAÑEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D16" t="n">
-        <v>-35.5239</v>
+        <v>-34.4304</v>
       </c>
       <c r="E16" t="n">
-        <v>-17.2283</v>
+        <v>-27.9249</v>
       </c>
       <c r="F16" t="n">
-        <v>-18.2957</v>
+        <v>-6.5056</v>
       </c>
       <c r="G16" t="n">
-        <v>-14.4272</v>
+        <v>-8.856200000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.3087</v>
+        <v>0.7115</v>
       </c>
       <c r="I16" t="n">
-        <v>-12.1186</v>
+        <v>-9.568100000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>11.8584</v>
+        <v>11.889</v>
       </c>
       <c r="K16" t="n">
-        <v>14.3918</v>
+        <v>15.7649</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.5334</v>
+        <v>-3.8758</v>
       </c>
       <c r="M16" t="n">
-        <v>-26.2859</v>
+        <v>-20.7456</v>
       </c>
       <c r="N16" t="n">
-        <v>-16.7004</v>
+        <v>-15.0534</v>
       </c>
       <c r="O16" t="n">
-        <v>-9.5855</v>
+        <v>-5.692299999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>6.7451</v>
+        <v>-13.0932</v>
       </c>
       <c r="Q16" t="n">
-        <v>-27.1786</v>
+        <v>-51.9764</v>
       </c>
       <c r="R16" t="n">
-        <v>33.9237</v>
+        <v>38.8833</v>
       </c>
       <c r="S16" t="n">
-        <v>-29.7927</v>
+        <v>-15.134</v>
       </c>
       <c r="T16" t="n">
-        <v>-12.1963</v>
+        <v>-7.1742</v>
       </c>
       <c r="U16" t="n">
-        <v>-17.5971</v>
+        <v>-7.96</v>
       </c>
       <c r="V16" t="n">
-        <v>1.9511</v>
+        <v>2.6532</v>
       </c>
       <c r="W16" t="n">
-        <v>10.288</v>
+        <v>19.3367</v>
       </c>
       <c r="X16" t="n">
-        <v>-8.3369</v>
+        <v>-16.6834</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>H. OLAGUIBE GONZALEZ</t>
+          <t>J. ESONO MBA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D17" t="n">
-        <v>-38.6435</v>
+        <v>-35.8544</v>
       </c>
       <c r="E17" t="n">
-        <v>-18.5589</v>
+        <v>-18.7384</v>
       </c>
       <c r="F17" t="n">
-        <v>-20.0847</v>
+        <v>-17.1163</v>
       </c>
       <c r="G17" t="n">
-        <v>-9.744299999999999</v>
+        <v>-15.2943</v>
       </c>
       <c r="H17" t="n">
-        <v>-5.1827</v>
+        <v>-7.811200000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-4.5617</v>
+        <v>-7.482900000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>21.8384</v>
+        <v>2.4129</v>
       </c>
       <c r="K17" t="n">
-        <v>16.439</v>
+        <v>-0.7199</v>
       </c>
       <c r="L17" t="n">
-        <v>5.3994</v>
+        <v>3.1327</v>
       </c>
       <c r="M17" t="n">
-        <v>-31.5825</v>
+        <v>-17.7069</v>
       </c>
       <c r="N17" t="n">
-        <v>-21.6214</v>
+        <v>-7.0913</v>
       </c>
       <c r="O17" t="n">
-        <v>-9.961</v>
+        <v>-10.6155</v>
       </c>
       <c r="P17" t="n">
-        <v>-12.4982</v>
+        <v>0.3968999999999996</v>
       </c>
       <c r="Q17" t="n">
-        <v>-45.4296</v>
+        <v>-30.749</v>
       </c>
       <c r="R17" t="n">
-        <v>32.932</v>
+        <v>31.1465</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.4092</v>
+        <v>1.7614</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9612999999999999</v>
+        <v>5.5562</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.4475</v>
+        <v>-3.7952</v>
       </c>
       <c r="V17" t="n">
-        <v>-13.9923</v>
+        <v>-22.7184</v>
       </c>
       <c r="W17" t="n">
-        <v>5.9941</v>
+        <v>4.0418</v>
       </c>
       <c r="X17" t="n">
-        <v>-19.9864</v>
+        <v>-26.7602</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. CRUZ JOBACHO</t>
+          <t>J. SERRA ANGLÈS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D18" t="n">
-        <v>-41.2185</v>
+        <v>-38.5903</v>
       </c>
       <c r="E18" t="n">
-        <v>-27.9811</v>
+        <v>-22.8934</v>
       </c>
       <c r="F18" t="n">
-        <v>-13.2377</v>
+        <v>-15.697</v>
       </c>
       <c r="G18" t="n">
-        <v>-23.4239</v>
+        <v>-15.2431</v>
       </c>
       <c r="H18" t="n">
-        <v>-12.4742</v>
+        <v>-10.2124</v>
       </c>
       <c r="I18" t="n">
-        <v>-10.9497</v>
+        <v>-5.0306</v>
       </c>
       <c r="J18" t="n">
-        <v>-4.7672</v>
+        <v>16.2088</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.7673000000000001</v>
+        <v>10.644</v>
       </c>
       <c r="L18" t="n">
-        <v>-4.000000000000001</v>
+        <v>5.5648</v>
       </c>
       <c r="M18" t="n">
-        <v>-18.6565</v>
+        <v>-31.4519</v>
       </c>
       <c r="N18" t="n">
-        <v>-11.707</v>
+        <v>-20.8564</v>
       </c>
       <c r="O18" t="n">
-        <v>-6.949400000000001</v>
+        <v>-10.5959</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7936</v>
+        <v>0.1983000000000001</v>
       </c>
       <c r="Q18" t="n">
-        <v>-26.1865</v>
+        <v>-43.2474</v>
       </c>
       <c r="R18" t="n">
-        <v>26.9804</v>
+        <v>43.4461</v>
       </c>
       <c r="S18" t="n">
-        <v>-7.6928</v>
+        <v>-14.4384</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7695999999999998</v>
+        <v>-8.165800000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-6.9237</v>
+        <v>-6.2724</v>
       </c>
       <c r="V18" t="n">
-        <v>-10.8952</v>
+        <v>-9.1074</v>
       </c>
       <c r="W18" t="n">
-        <v>3.7429</v>
+        <v>12.3113</v>
       </c>
       <c r="X18" t="n">
-        <v>-14.6379</v>
+        <v>-21.4187</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. GARCIA IBAÑEZ</t>
+          <t>H. OLAGUIBE GONZALEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>23</v>
       </c>
       <c r="D19" t="n">
-        <v>-42.7918</v>
+        <v>-41.591</v>
       </c>
       <c r="E19" t="n">
-        <v>-32.9131</v>
+        <v>-21.2005</v>
       </c>
       <c r="F19" t="n">
-        <v>-9.879200000000001</v>
+        <v>-20.3906</v>
       </c>
       <c r="G19" t="n">
-        <v>-8.856200000000001</v>
+        <v>-9.744299999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7115</v>
+        <v>-5.1827</v>
       </c>
       <c r="I19" t="n">
-        <v>-9.568100000000001</v>
+        <v>-4.5617</v>
       </c>
       <c r="J19" t="n">
-        <v>11.889</v>
+        <v>21.8384</v>
       </c>
       <c r="K19" t="n">
-        <v>15.7649</v>
+        <v>16.439</v>
       </c>
       <c r="L19" t="n">
-        <v>-3.8758</v>
+        <v>5.3994</v>
       </c>
       <c r="M19" t="n">
-        <v>-20.7456</v>
+        <v>-31.5825</v>
       </c>
       <c r="N19" t="n">
-        <v>-15.0534</v>
+        <v>-21.6214</v>
       </c>
       <c r="O19" t="n">
-        <v>-5.692299999999999</v>
+        <v>-9.961</v>
       </c>
       <c r="P19" t="n">
-        <v>-13.0932</v>
+        <v>-12.4982</v>
       </c>
       <c r="Q19" t="n">
-        <v>-51.9764</v>
+        <v>-45.4296</v>
       </c>
       <c r="R19" t="n">
-        <v>38.8833</v>
+        <v>32.932</v>
       </c>
       <c r="S19" t="n">
-        <v>-23.4953</v>
+        <v>-5.356400000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-12.1621</v>
+        <v>-3.6028</v>
       </c>
       <c r="U19" t="n">
-        <v>-11.3335</v>
+        <v>-1.7538</v>
       </c>
       <c r="V19" t="n">
-        <v>2.6532</v>
+        <v>-13.9923</v>
       </c>
       <c r="W19" t="n">
-        <v>19.3367</v>
+        <v>5.9941</v>
       </c>
       <c r="X19" t="n">
-        <v>-16.6834</v>
+        <v>-19.9864</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. SERRA ANGLÈS</t>
+          <t>A. CRUZ JOBACHO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,70 +1966,70 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D20" t="n">
-        <v>-48.7341</v>
+        <v>-44.8536</v>
       </c>
       <c r="E20" t="n">
-        <v>-29.508</v>
+        <v>-29.931</v>
       </c>
       <c r="F20" t="n">
-        <v>-19.2261</v>
+        <v>-14.9224</v>
       </c>
       <c r="G20" t="n">
-        <v>-15.2431</v>
+        <v>-23.4239</v>
       </c>
       <c r="H20" t="n">
-        <v>-10.2124</v>
+        <v>-12.4742</v>
       </c>
       <c r="I20" t="n">
-        <v>-5.0306</v>
+        <v>-10.9497</v>
       </c>
       <c r="J20" t="n">
-        <v>16.2088</v>
+        <v>-4.7672</v>
       </c>
       <c r="K20" t="n">
-        <v>10.644</v>
+        <v>-0.7673000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>5.5648</v>
+        <v>-4.000000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>-31.4519</v>
+        <v>-18.6565</v>
       </c>
       <c r="N20" t="n">
-        <v>-20.8564</v>
+        <v>-11.707</v>
       </c>
       <c r="O20" t="n">
-        <v>-10.5959</v>
+        <v>-6.949400000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1983000000000001</v>
+        <v>0.7936</v>
       </c>
       <c r="Q20" t="n">
-        <v>-43.2474</v>
+        <v>-26.1865</v>
       </c>
       <c r="R20" t="n">
-        <v>43.4461</v>
+        <v>26.9804</v>
       </c>
       <c r="S20" t="n">
-        <v>-24.5822</v>
+        <v>-11.3278</v>
       </c>
       <c r="T20" t="n">
-        <v>-14.7804</v>
+        <v>-2.7193</v>
       </c>
       <c r="U20" t="n">
-        <v>-9.801500000000001</v>
+        <v>-8.608499999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>-9.1074</v>
+        <v>-10.8952</v>
       </c>
       <c r="W20" t="n">
-        <v>12.3113</v>
+        <v>3.7429</v>
       </c>
       <c r="X20" t="n">
-        <v>-21.4187</v>
+        <v>-14.6379</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>25</v>
       </c>
       <c r="D21" t="n">
-        <v>-320.4097</v>
+        <v>-298.505</v>
       </c>
       <c r="E21" t="n">
-        <v>-203.0131</v>
+        <v>-193.3498</v>
       </c>
       <c r="F21" t="n">
-        <v>-117.3987</v>
+        <v>-105.1546</v>
       </c>
       <c r="G21" t="n">
         <v>-135.0702</v>
@@ -2071,7 +2071,7 @@
         <v>103.3564</v>
       </c>
       <c r="L21" t="n">
-        <v>49.3749</v>
+        <v>49.37489999999999</v>
       </c>
       <c r="M21" t="n">
         <v>-287.8027</v>
@@ -2083,25 +2083,25 @@
         <v>-109.9074</v>
       </c>
       <c r="P21" t="n">
-        <v>4.9605</v>
+        <v>4.960499999999998</v>
       </c>
       <c r="Q21" t="n">
-        <v>-420.5715</v>
+        <v>-420.5715000000001</v>
       </c>
       <c r="R21" t="n">
         <v>425.5346</v>
       </c>
       <c r="S21" t="n">
-        <v>-139.0108</v>
+        <v>-117.1042</v>
       </c>
       <c r="T21" t="n">
-        <v>-60.7395</v>
+        <v>-51.07660000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-78.2714</v>
+        <v>-66.02849999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>-51.289</v>
+        <v>-51.28899999999999</v>
       </c>
       <c r="W21" t="n">
         <v>125.57</v>
